--- a/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
@@ -496,22 +496,22 @@
         <v>2.162892233170064</v>
       </c>
       <c r="E2" t="n">
-        <v>1.929674856451603</v>
+        <v>1.929674856451602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040978</v>
+        <v>0.1035855209040977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860989</v>
+        <v>0.007426784120860984</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444222e-05</v>
+        <v>6.745209067444211e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001137574516857956</v>
+        <v>0.00113757451685795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000450859705</v>
+        <v>0.1210000450859714</v>
       </c>
     </row>
     <row r="3">
@@ -532,22 +532,22 @@
         <v>2.150956348841236</v>
       </c>
       <c r="E3" t="n">
-        <v>1.919906209680579</v>
+        <v>1.919906209680578</v>
       </c>
       <c r="F3" t="n">
         <v>0.1015010861438635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810821</v>
+        <v>0.007384459751810814</v>
       </c>
       <c r="H3" t="n">
-        <v>6.54844449954689e-05</v>
+        <v>6.548444499546888e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00109906403938336</v>
+        <v>0.001099064039383354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000447806041</v>
+        <v>0.121000044780605</v>
       </c>
     </row>
     <row r="4">
@@ -568,22 +568,22 @@
         <v>2.135174309015724</v>
       </c>
       <c r="E4" t="n">
-        <v>1.908918085438748</v>
+        <v>1.908918085438749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761515</v>
+        <v>0.09677604689761529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928324</v>
+        <v>0.007353794018928255</v>
       </c>
       <c r="H4" t="n">
-        <v>6.550986959197539e-05</v>
+        <v>6.55098695919754e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001060828464859125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.121000044325982</v>
+        <v>0.1210000443259802</v>
       </c>
     </row>
     <row r="5">
@@ -604,22 +604,22 @@
         <v>2.106457689119131</v>
       </c>
       <c r="E5" t="n">
-        <v>1.889999394546655</v>
+        <v>1.889999394546654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0871102725366628</v>
+        <v>0.08711027253666284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543527</v>
+        <v>0.007277042766543525</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856547e-05</v>
+        <v>6.531025410856539e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878538</v>
+        <v>0.001005625542878534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000434722829</v>
+        <v>0.1210000434722833</v>
       </c>
     </row>
     <row r="6">
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.928161429538936</v>
+        <v>1.928161429538937</v>
       </c>
       <c r="E6" t="n">
-        <v>1.771550223398428</v>
+        <v>1.771550223398427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442238</v>
+        <v>0.02782467977442239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621233</v>
+        <v>0.006933990820621253</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626458e-05</v>
+        <v>5.328554056626459e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159822952</v>
+        <v>0.0007992118159823028</v>
       </c>
       <c r="J6" t="n">
-        <v>0.121000038188916</v>
+        <v>0.1210000381889176</v>
       </c>
     </row>
     <row r="7">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.864864304589706</v>
+        <v>1.864864304589707</v>
       </c>
       <c r="E7" t="n">
         <v>1.728080311849935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099382</v>
+        <v>0.008197098928099425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006824718527754085</v>
+        <v>0.0068247185277541</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013729e-05</v>
+        <v>5.058758619013724e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757357</v>
+        <v>0.0007115513488757329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000363488524</v>
+        <v>0.1210000363488533</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.84363825071023</v>
+        <v>1.843638250710229</v>
       </c>
       <c r="E8" t="n">
-        <v>1.711965309812021</v>
+        <v>1.71196530981202</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732839</v>
+        <v>0.003188815024732812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817043</v>
+        <v>0.006763638394817044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413859e-05</v>
+        <v>4.944316302413858e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970081</v>
+        <v>0.0006710085431970094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000357724386</v>
+        <v>0.1210000357724377</v>
       </c>
     </row>
     <row r="9">
@@ -751,16 +751,16 @@
         <v>1.882182601483586</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120162</v>
+        <v>0.08349467576120159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00729577678843515</v>
+        <v>0.007295776788435114</v>
       </c>
       <c r="H9" t="n">
-        <v>6.318339027118057e-05</v>
+        <v>6.31833902711806e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839521</v>
+        <v>0.001025281633839523</v>
       </c>
       <c r="J9" t="n">
         <v>0.1210000431383778</v>
@@ -784,19 +784,19 @@
         <v>1.962639653431731</v>
       </c>
       <c r="E10" t="n">
-        <v>1.795858450823423</v>
+        <v>1.795858450823424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602936</v>
+        <v>0.03770430310602928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626196</v>
+        <v>0.007124428452626189</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367424e-05</v>
+        <v>5.859710161367419e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770118</v>
+        <v>0.0008938347806770122</v>
       </c>
       <c r="J10" t="n">
         <v>0.1210000391673611</v>
@@ -820,22 +820,22 @@
         <v>1.864023897287264</v>
       </c>
       <c r="E11" t="n">
-        <v>1.729668873957567</v>
+        <v>1.729668873957568</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005756448789606221</v>
+        <v>0.00575644878960622</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006820789933289952</v>
+        <v>0.00682078993329</v>
       </c>
       <c r="H11" t="n">
         <v>5.136640220355119e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007263819355289015</v>
+        <v>0.000726381935528901</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000362690691</v>
+        <v>0.1210000362690673</v>
       </c>
     </row>
   </sheetData>
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.446239705381318</v>
+        <v>1.446239705381317</v>
       </c>
       <c r="E2" t="n">
-        <v>1.213022343856727</v>
+        <v>1.213022343856726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040978</v>
+        <v>0.1035855209040977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860989</v>
+        <v>0.007426784120860984</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444222e-05</v>
+        <v>6.745209067444211e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001137574516857956</v>
+        <v>0.00113757451685795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000298920999</v>
+        <v>0.1210000298920995</v>
       </c>
     </row>
     <row r="3">
@@ -953,19 +953,19 @@
         <v>1.430915495328006</v>
       </c>
       <c r="E3" t="n">
-        <v>1.199865371433063</v>
+        <v>1.199865371433064</v>
       </c>
       <c r="F3" t="n">
         <v>0.1015010861438635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810821</v>
+        <v>0.007384459751810814</v>
       </c>
       <c r="H3" t="n">
-        <v>6.54844449954689e-05</v>
+        <v>6.548444499546888e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00109906403938336</v>
+        <v>0.001099064039383354</v>
       </c>
       <c r="J3" t="n">
         <v>0.1210000295148894</v>
@@ -989,22 +989,22 @@
         <v>1.404129244304243</v>
       </c>
       <c r="E4" t="n">
-        <v>1.17787303622628</v>
+        <v>1.177873036226281</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761515</v>
+        <v>0.09677604689761529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928324</v>
+        <v>0.007353794018928255</v>
       </c>
       <c r="H4" t="n">
-        <v>6.550986959197539e-05</v>
+        <v>6.55098695919754e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001060828464859125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000288269675</v>
+        <v>0.121000028826967</v>
       </c>
     </row>
     <row r="5">
@@ -1028,19 +1028,19 @@
         <v>1.13645622755587</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0871102725366628</v>
+        <v>0.08711027253666284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543527</v>
+        <v>0.007277042766543525</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856547e-05</v>
+        <v>6.531025410856539e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878538</v>
+        <v>0.001005625542878534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121000027496283</v>
+        <v>0.1210000274962832</v>
       </c>
     </row>
     <row r="6">
@@ -1061,19 +1061,19 @@
         <v>1.02926986694864</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8726586798656931</v>
+        <v>0.8726586798656926</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442238</v>
+        <v>0.02782467977442239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621233</v>
+        <v>0.006933990820621253</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626458e-05</v>
+        <v>5.328554056626459e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159822952</v>
+        <v>0.0007992118159823028</v>
       </c>
       <c r="J6" t="n">
         <v>0.1210000191313552</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9185080915392773</v>
+        <v>0.9185080915392779</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7817241188633723</v>
+        <v>0.7817241188633747</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099382</v>
+        <v>0.008197098928099425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006824718527754085</v>
+        <v>0.0068247185277541</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013729e-05</v>
+        <v>5.058758619013724e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757357</v>
+        <v>0.0007115513488757329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000162849856</v>
+        <v>0.1210000162849839</v>
       </c>
     </row>
     <row r="8">
@@ -1130,25 +1130,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8870995442684119</v>
+        <v>0.8870995442684114</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7554266236499459</v>
+        <v>0.7554266236499462</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732839</v>
+        <v>0.003188815024732812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817043</v>
+        <v>0.006763638394817044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413859e-05</v>
+        <v>4.944316302413858e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970081</v>
+        <v>0.0006710085431970094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000154926948</v>
+        <v>0.1210000154926942</v>
       </c>
     </row>
     <row r="9">
@@ -1169,22 +1169,22 @@
         <v>1.331348518706898</v>
       </c>
       <c r="E9" t="n">
-        <v>1.118469574186389</v>
+        <v>1.118469574186388</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120162</v>
+        <v>0.08349467576120159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00729577678843515</v>
+        <v>0.007295776788435114</v>
       </c>
       <c r="H9" t="n">
-        <v>6.318339027118057e-05</v>
+        <v>6.31833902711806e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839521</v>
+        <v>0.001025281633839523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000269467613</v>
+        <v>0.1210000269467624</v>
       </c>
     </row>
     <row r="10">
@@ -1205,22 +1205,22 @@
         <v>1.08464494007742</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9178637560836347</v>
+        <v>0.917863756083633</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602936</v>
+        <v>0.03770430310602928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626196</v>
+        <v>0.007124428452626189</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367424e-05</v>
+        <v>5.859710161367419e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770118</v>
+        <v>0.0008938347806770122</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000205528389</v>
+        <v>0.1210000205528406</v>
       </c>
     </row>
     <row r="11">
@@ -1238,25 +1238,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9102668654220011</v>
+        <v>0.9102668654220004</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7759118623130737</v>
+        <v>0.7759118623130734</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005756448789606221</v>
+        <v>0.00575644878960622</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006820789933289952</v>
+        <v>0.00682078993329</v>
       </c>
       <c r="H11" t="n">
         <v>5.136640220355119e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007263819355289015</v>
+        <v>0.000726381935528901</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000160482987</v>
+        <v>0.1210000160482982</v>
       </c>
     </row>
   </sheetData>
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.700721610298002</v>
+        <v>-1.70072161029792</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.933938905103372</v>
+        <v>-1.933938905103299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040978</v>
+        <v>0.1035855209040977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860989</v>
+        <v>0.007426784120860984</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444222e-05</v>
+        <v>6.745209067444211e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001137574516857956</v>
+        <v>0.00113757451685795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999631728795</v>
+        <v>0.1209999631728884</v>
       </c>
     </row>
     <row r="3">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.837338465435598</v>
+        <v>-1.837338465435544</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.068388520039813</v>
+        <v>-2.068388520039496</v>
       </c>
       <c r="F3" t="n">
         <v>0.1015010861438635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810821</v>
+        <v>0.007384459751810814</v>
       </c>
       <c r="H3" t="n">
-        <v>6.54844449954689e-05</v>
+        <v>6.548444499546888e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00109906403938336</v>
+        <v>0.001099064039383354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999602241618</v>
+        <v>0.1209999602238991</v>
       </c>
     </row>
     <row r="4">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.976232372337928</v>
+        <v>-1.976232372337886</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.202488508748194</v>
+        <v>-2.202488508748171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761515</v>
+        <v>0.09677604689761529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928324</v>
+        <v>0.007353794018928255</v>
       </c>
       <c r="H4" t="n">
-        <v>6.550986959197539e-05</v>
+        <v>6.55098695919754e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001060828464859125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999571592704</v>
+        <v>0.1209999571592899</v>
       </c>
     </row>
     <row r="5">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.10936570206554</v>
+        <v>-2.10936570206544</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.325823907257487</v>
+        <v>-2.325823907257495</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0871102725366628</v>
+        <v>0.08711027253666284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543527</v>
+        <v>0.007277042766543525</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856547e-05</v>
+        <v>6.531025410856539e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878538</v>
+        <v>0.001005625542878534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999540917539</v>
+        <v>0.1209999540918609</v>
       </c>
     </row>
     <row r="6">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.842569766613962</v>
+        <v>-2.84256976661365</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.99918087160977</v>
+        <v>-2.999180871609115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442238</v>
+        <v>0.02782467977442239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621233</v>
+        <v>0.006933990820621253</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626458e-05</v>
+        <v>5.328554056626459e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159822952</v>
+        <v>0.0007992118159823028</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999370442159</v>
+        <v>0.1209999370438735</v>
       </c>
     </row>
     <row r="7">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.166135057324487</v>
+        <v>-3.166135057324498</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.302918943401175</v>
+        <v>-3.302918943401294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099382</v>
+        <v>0.008197098928099425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006824718527754085</v>
+        <v>0.0068247185277541</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013729e-05</v>
+        <v>5.058758619013724e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757357</v>
+        <v>0.0007115513488757329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999296857691</v>
+        <v>0.1209999296858757</v>
       </c>
     </row>
     <row r="8">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.266560753660541</v>
+        <v>-3.266560753660517</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.398233586216459</v>
+        <v>-3.398233586216479</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732839</v>
+        <v>0.003188815024732812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817043</v>
+        <v>0.006763638394817044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413859e-05</v>
+        <v>4.944316302413858e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970081</v>
+        <v>0.0006710085431970094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999274301472</v>
+        <v>0.1209999274301907</v>
       </c>
     </row>
     <row r="9">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.122292065063064</v>
+        <v>-2.122292065062914</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.335170936362246</v>
+        <v>-2.335170936362396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120162</v>
+        <v>0.08349467576120159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00729577678843515</v>
+        <v>0.007295776788435114</v>
       </c>
       <c r="H9" t="n">
-        <v>6.318339027118057e-05</v>
+        <v>6.31833902711806e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839521</v>
+        <v>0.001025281633839523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999537254345</v>
+        <v>0.1209999537257347</v>
       </c>
     </row>
     <row r="10">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.741163168163472</v>
+        <v>-2.741163168163421</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.907944271045609</v>
+        <v>-2.907944271045579</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602936</v>
+        <v>0.03770430310602928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626196</v>
+        <v>0.007124428452626189</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367424e-05</v>
+        <v>5.859710161367419e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770118</v>
+        <v>0.0008938347806770122</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999394411905</v>
+        <v>0.1209999394412113</v>
       </c>
     </row>
     <row r="11">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.128283276871664</v>
+        <v>-3.128283276871695</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.262638194358608</v>
+        <v>-3.2626381943586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005756448789606221</v>
+        <v>0.00575644878960622</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006820789933289952</v>
+        <v>0.00682078993329</v>
       </c>
       <c r="H11" t="n">
         <v>5.136640220355119e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007263819355289015</v>
+        <v>0.000726381935528901</v>
       </c>
       <c r="J11" t="n">
-        <v>0.120999930426315</v>
+        <v>0.1209999304262754</v>
       </c>
     </row>
   </sheetData>
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.078755569426401</v>
+        <v>-1.078755569426559</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.311972877418203</v>
+        <v>-1.311972877418286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040978</v>
+        <v>0.1035855209040977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860989</v>
+        <v>0.007426784120860984</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444222e-05</v>
+        <v>6.745209067444211e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001137574516857956</v>
+        <v>0.00113757451685795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999763593108</v>
+        <v>0.1209999763592355</v>
       </c>
     </row>
     <row r="3">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.378189043694227</v>
+        <v>-1.378189043694081</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.609239108032847</v>
+        <v>-1.609239108032824</v>
       </c>
       <c r="F3" t="n">
         <v>0.1015010861438635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810821</v>
+        <v>0.007384459751810814</v>
       </c>
       <c r="H3" t="n">
-        <v>6.54844449954689e-05</v>
+        <v>6.548444499546888e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00109906403938336</v>
+        <v>0.001099064039383354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999699585669</v>
+        <v>0.1209999699586899</v>
       </c>
     </row>
     <row r="4">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.601287658722041</v>
+        <v>-1.601287658722098</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.827543803081637</v>
+        <v>-1.827543803081649</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761515</v>
+        <v>0.09677604689761529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928324</v>
+        <v>0.007353794018928255</v>
       </c>
       <c r="H4" t="n">
-        <v>6.550986959197539e-05</v>
+        <v>6.55098695919754e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001060828464859125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999651086011</v>
+        <v>0.120999965108556</v>
       </c>
     </row>
     <row r="5">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.791296104189162</v>
+        <v>-1.791296104189118</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0077543161246</v>
+        <v>-2.007754316124651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0871102725366628</v>
+        <v>0.08711027253666284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543527</v>
+        <v>0.007277042766543525</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856547e-05</v>
+        <v>6.531025410856539e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878538</v>
+        <v>0.001005625542878534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999608352441</v>
+        <v>0.1209999608353387</v>
       </c>
     </row>
     <row r="6">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.571897764042288</v>
+        <v>-2.571897764041717</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.728508874776175</v>
+        <v>-2.72850887477563</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442238</v>
+        <v>0.02782467977442239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621233</v>
+        <v>0.006933990820621253</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626458e-05</v>
+        <v>5.328554056626459e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159822952</v>
+        <v>0.0007992118159823028</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999427822948</v>
+        <v>0.120999942782321</v>
       </c>
     </row>
     <row r="7">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.957954152714162</v>
+        <v>-2.957954152714411</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.094738043204581</v>
+        <v>-3.094738043204731</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099382</v>
+        <v>0.008197098928099425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006824718527754085</v>
+        <v>0.0068247185277541</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013729e-05</v>
+        <v>5.058758619013724e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757357</v>
+        <v>0.0007115513488757329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999340994994</v>
+        <v>0.1209999340994004</v>
       </c>
     </row>
     <row r="8">
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.085793088020575</v>
+        <v>-3.085793088020571</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.217465924408992</v>
+        <v>-3.217465924409018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732839</v>
+        <v>0.003188815024732812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817043</v>
+        <v>0.006763638394817044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413859e-05</v>
+        <v>4.944316302413858e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970081</v>
+        <v>0.0006710085431970094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.120999931262646</v>
+        <v>0.1209999312626766</v>
       </c>
     </row>
     <row r="9">
@@ -2008,25 +2008,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.682490535293208</v>
+        <v>-1.682490535293083</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.895369415916737</v>
+        <v>-1.895369415916696</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120162</v>
+        <v>0.08349467576120159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00729577678843515</v>
+        <v>0.007295776788435114</v>
       </c>
       <c r="H9" t="n">
-        <v>6.318339027118057e-05</v>
+        <v>6.31833902711806e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839521</v>
+        <v>0.001025281633839523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999630497816</v>
+        <v>0.1209999630498659</v>
       </c>
     </row>
     <row r="10">
@@ -2044,25 +2044,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.416226594552516</v>
+        <v>-2.416226594552518</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.583007704323758</v>
+        <v>-2.583007704323732</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602936</v>
+        <v>0.03770430310602928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626196</v>
+        <v>0.007124428452626189</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367424e-05</v>
+        <v>5.859710161367419e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770118</v>
+        <v>0.0008938347806770122</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999463302953</v>
+        <v>0.1209999463302669</v>
       </c>
     </row>
     <row r="11">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.088327305284082</v>
+        <v>-3.088327305284071</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.222682223618091</v>
+        <v>-3.222682223618108</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005756448789606221</v>
+        <v>0.00575644878960622</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006820789933289952</v>
+        <v>0.00682078993329</v>
       </c>
       <c r="H11" t="n">
         <v>5.136640220355119e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007263819355289015</v>
+        <v>0.000726381935528901</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999312733805</v>
+        <v>0.1209999312734085</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.162892233170064</v>
+        <v>2.141035566516668</v>
       </c>
       <c r="E2" t="n">
-        <v>1.929674856451602</v>
+        <v>1.914733173317971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040977</v>
+        <v>0.09678259603512485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860984</v>
+        <v>0.007360584415200119</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444211e-05</v>
+        <v>6.59915156572896e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00113757451685795</v>
+        <v>0.001093176782134807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000450859714</v>
+        <v>0.1210000444505801</v>
       </c>
     </row>
     <row r="3">
@@ -529,25 +529,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.150956348841236</v>
+        <v>2.124140124465378</v>
       </c>
       <c r="E3" t="n">
-        <v>1.919906209680578</v>
+        <v>1.901540325719272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1015010861438635</v>
+        <v>0.09317211825438219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810814</v>
+        <v>0.007311495997932799</v>
       </c>
       <c r="H3" t="n">
-        <v>6.548444499546888e-05</v>
+        <v>6.382090465884193e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001099064039383354</v>
+        <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.121000044780605</v>
+        <v>0.1210000440013377</v>
       </c>
     </row>
     <row r="4">
@@ -565,25 +565,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.135174309015724</v>
+        <v>2.10681000661595</v>
       </c>
       <c r="E4" t="n">
-        <v>1.908918085438749</v>
+        <v>1.889099615459105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761529</v>
+        <v>0.08835730183707283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928255</v>
+        <v>0.007276274024719108</v>
       </c>
       <c r="H4" t="n">
-        <v>6.55098695919754e-05</v>
+        <v>6.376829510261294e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001060828464859125</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000443259802</v>
+        <v>0.1210000435117131</v>
       </c>
     </row>
     <row r="5">
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.106457689119131</v>
+        <v>2.082490632459138</v>
       </c>
       <c r="E5" t="n">
-        <v>1.889999394546654</v>
+        <v>1.872829494262928</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08711027253666284</v>
+        <v>0.08042508548545475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543525</v>
+        <v>0.007207831033124094</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856539e-05</v>
+        <v>6.386321456211526e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878534</v>
+        <v>0.0009643156678152186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000434722833</v>
+        <v>0.121000042795254</v>
       </c>
     </row>
     <row r="6">
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.928161429538937</v>
+        <v>1.914707854784179</v>
       </c>
       <c r="E6" t="n">
-        <v>1.771550223398427</v>
+        <v>1.760426132282819</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442239</v>
+        <v>0.02556995385670486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621253</v>
+        <v>0.006892784966531855</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626459e-05</v>
+        <v>5.236811283617112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159823028</v>
+        <v>0.0007665777182855944</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000381889176</v>
+        <v>0.1210000378470011</v>
       </c>
     </row>
     <row r="7">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.864864304589707</v>
+        <v>1.854429677059307</v>
       </c>
       <c r="E7" t="n">
-        <v>1.728080311849935</v>
+        <v>1.718160740997224</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099425</v>
+        <v>0.007740537116147202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068247185277541</v>
+        <v>0.006794605080025641</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013724e-05</v>
+        <v>4.994743146261051e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757329</v>
+        <v>0.0006838103179389185</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000363488533</v>
+        <v>0.1210000361165082</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.843638250710229</v>
+        <v>1.835195175894396</v>
       </c>
       <c r="E8" t="n">
-        <v>1.71196530981202</v>
+        <v>1.703826476595302</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732812</v>
+        <v>0.002929998153368313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817044</v>
+        <v>0.006741165419815814</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413858e-05</v>
+        <v>4.897357410629079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970094</v>
+        <v>0.0006485265645910469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000357724377</v>
+        <v>0.1210000355872125</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.095061562195711</v>
+        <v>2.067952962974462</v>
       </c>
       <c r="E9" t="n">
-        <v>1.882182601483586</v>
+        <v>1.863092962298436</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120159</v>
+        <v>0.07560197571260402</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007295776788435114</v>
+        <v>0.007220209186640569</v>
       </c>
       <c r="H9" t="n">
-        <v>6.31833902711806e-05</v>
+        <v>6.140793176238142e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839523</v>
+        <v>0.0009763654809467796</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000431383778</v>
+        <v>0.1210000423640722</v>
       </c>
     </row>
     <row r="10">
@@ -781,25 +781,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.962639653431731</v>
+        <v>1.939107922231703</v>
       </c>
       <c r="E10" t="n">
-        <v>1.795858450823424</v>
+        <v>1.777853700417632</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602928</v>
+        <v>0.03230111592600439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626189</v>
+        <v>0.007049964221656469</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367419e-05</v>
+        <v>5.683386960572569e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770122</v>
+        <v>0.0008462692644841026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000391673611</v>
+        <v>0.1210000385323198</v>
       </c>
     </row>
     <row r="11">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.864023897287264</v>
+        <v>1.855643254487145</v>
       </c>
       <c r="E11" t="n">
-        <v>1.729668873957568</v>
+        <v>1.721522999261031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00575644878960622</v>
+        <v>0.00556556873205253</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00682078993329</v>
+        <v>0.006801557732157556</v>
       </c>
       <c r="H11" t="n">
-        <v>5.136640220355119e-05</v>
+        <v>5.102742425733942e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000726381935528901</v>
+        <v>0.000702065250868961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000362690673</v>
+        <v>0.1210000360867771</v>
       </c>
     </row>
   </sheetData>
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.446239705381317</v>
+        <v>1.408386574731458</v>
       </c>
       <c r="E2" t="n">
-        <v>1.213022343856726</v>
+        <v>1.182084197065787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040977</v>
+        <v>0.09678259603512485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860984</v>
+        <v>0.007360584415200119</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444211e-05</v>
+        <v>6.59915156572896e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00113757451685795</v>
+        <v>0.001093176782134807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000298920995</v>
+        <v>0.1210000289175541</v>
       </c>
     </row>
     <row r="3">
@@ -950,25 +950,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.430915495328006</v>
+        <v>1.384180269173959</v>
       </c>
       <c r="E3" t="n">
-        <v>1.199865371433064</v>
+        <v>1.161580486115878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1015010861438635</v>
+        <v>0.09317211825438219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810814</v>
+        <v>0.007311495997932799</v>
       </c>
       <c r="H3" t="n">
-        <v>6.548444499546888e-05</v>
+        <v>6.382090465884193e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001099064039383354</v>
+        <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000295148894</v>
+        <v>0.121000028313313</v>
       </c>
     </row>
     <row r="4">
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.404129244304243</v>
+        <v>1.355731181612598</v>
       </c>
       <c r="E4" t="n">
-        <v>1.177873036226281</v>
+        <v>1.138020806379505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761529</v>
+        <v>0.08835730183707283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928255</v>
+        <v>0.007276274024719108</v>
       </c>
       <c r="H4" t="n">
-        <v>6.55098695919754e-05</v>
+        <v>6.376829510261294e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001060828464859125</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.121000028826967</v>
+        <v>0.1210000275879606</v>
       </c>
     </row>
     <row r="5">
@@ -1022,25 +1022,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.352914506152347</v>
+        <v>1.313157161422697</v>
       </c>
       <c r="E5" t="n">
-        <v>1.13645622755587</v>
+        <v>1.103496039537263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08711027253666284</v>
+        <v>0.08042508548545475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543525</v>
+        <v>0.007207831033124094</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856539e-05</v>
+        <v>6.386321456211526e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878534</v>
+        <v>0.0009643156678152186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000274962832</v>
+        <v>0.1210000264844782</v>
       </c>
     </row>
     <row r="6">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02926986694864</v>
+        <v>1.011279632097182</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8726586798656926</v>
+        <v>0.8569979287495623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442239</v>
+        <v>0.02556995385670486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621253</v>
+        <v>0.006892784966531855</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626459e-05</v>
+        <v>5.236811283617112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159823028</v>
+        <v>0.0007665777182855944</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000191313552</v>
+        <v>0.1210000186932609</v>
       </c>
     </row>
     <row r="7">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9185080915392779</v>
+        <v>0.9081448545472069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7817241188633747</v>
+        <v>0.7718759385474721</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099425</v>
+        <v>0.007740537116147202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068247185277541</v>
+        <v>0.006794605080025641</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013724e-05</v>
+        <v>4.994743146261051e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757329</v>
+        <v>0.0006838103179389185</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000162849839</v>
+        <v>0.1210000160541606</v>
       </c>
     </row>
     <row r="8">
@@ -1130,25 +1130,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8870995442684114</v>
+        <v>0.878874847889285</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7554266236499462</v>
+        <v>0.7475061688653075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732812</v>
+        <v>0.002929998153368313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817044</v>
+        <v>0.006741165419815814</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413858e-05</v>
+        <v>4.897357410629079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970094</v>
+        <v>0.0006485265645910469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000154926942</v>
+        <v>0.121000015312096</v>
       </c>
     </row>
     <row r="9">
@@ -1166,25 +1166,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.331348518706898</v>
+        <v>1.285591915371015</v>
       </c>
       <c r="E9" t="n">
-        <v>1.118469574186388</v>
+        <v>1.080731931281963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120159</v>
+        <v>0.07560197571260402</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007295776788435114</v>
+        <v>0.007220209186640569</v>
       </c>
       <c r="H9" t="n">
-        <v>6.31833902711806e-05</v>
+        <v>6.140793176238142e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839523</v>
+        <v>0.0009763654809467796</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000269467624</v>
+        <v>0.1210000257770985</v>
       </c>
     </row>
     <row r="10">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.08464494007742</v>
+        <v>1.049040512915575</v>
       </c>
       <c r="E10" t="n">
-        <v>0.917863756083633</v>
+        <v>0.8877863099719849</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602928</v>
+        <v>0.03230111592600439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626189</v>
+        <v>0.007049964221656469</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367419e-05</v>
+        <v>5.683386960572569e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770122</v>
+        <v>0.0008462692644841026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000205528406</v>
+        <v>0.1210000196618395</v>
       </c>
     </row>
     <row r="11">
@@ -1238,25 +1238,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9102668654220004</v>
+        <v>0.9020524648194492</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7759118623130734</v>
+        <v>0.7679322298105761</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00575644878960622</v>
+        <v>0.00556556873205253</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00682078993329</v>
+        <v>0.006801557732157556</v>
       </c>
       <c r="H11" t="n">
-        <v>5.136640220355119e-05</v>
+        <v>5.102742425733942e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000726381935528901</v>
+        <v>0.000702065250868961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000160482982</v>
+        <v>0.1210000158695369</v>
       </c>
     </row>
   </sheetData>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.70072161029792</v>
+        <v>-1.913735852460093</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.933938905103299</v>
+        <v>-2.140038159692896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040977</v>
+        <v>0.09678259603512485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860984</v>
+        <v>0.007360584415200119</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444211e-05</v>
+        <v>6.59915156572896e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00113757451685795</v>
+        <v>0.001093176782134807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999631728884</v>
+        <v>0.1209999584846859</v>
       </c>
     </row>
     <row r="3">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.837338465435544</v>
+        <v>-2.066027288397335</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.068388520039496</v>
+        <v>-2.288626998306958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1015010861438635</v>
+        <v>0.09317211825438219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810814</v>
+        <v>0.007311495997932799</v>
       </c>
       <c r="H3" t="n">
-        <v>6.548444499546888e-05</v>
+        <v>6.382090465884193e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001099064039383354</v>
+        <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999602238991</v>
+        <v>0.1209999551648555</v>
       </c>
     </row>
     <row r="4">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.976232372337886</v>
+        <v>-2.196242301074677</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.202488508748171</v>
+        <v>-2.413952601001734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761529</v>
+        <v>0.08835730183707283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928255</v>
+        <v>0.007276274024719108</v>
       </c>
       <c r="H4" t="n">
-        <v>6.55098695919754e-05</v>
+        <v>6.376829510261294e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001060828464859125</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999571592899</v>
+        <v>0.1209999522819252</v>
       </c>
     </row>
     <row r="5">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.10936570206544</v>
+        <v>-2.290140281347844</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.325823907257495</v>
+        <v>-2.499801326839144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08711027253666284</v>
+        <v>0.08042508548545475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543525</v>
+        <v>0.007207831033124094</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856539e-05</v>
+        <v>6.386321456211526e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878534</v>
+        <v>0.0009643156678152186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999540918609</v>
+        <v>0.1209999500903445</v>
       </c>
     </row>
     <row r="6">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.84256976661365</v>
+        <v>-2.95144306735271</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.999180871609115</v>
+        <v>-3.105724686685964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442239</v>
+        <v>0.02556995385670486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621253</v>
+        <v>0.006892784966531855</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626459e-05</v>
+        <v>5.236811283617112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159823028</v>
+        <v>0.0007665777182855944</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999370438735</v>
+        <v>0.120999934678895</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.166135057324498</v>
+        <v>-3.238392115823753</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.302918943401294</v>
+        <v>-3.374660943912011</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099425</v>
+        <v>0.007740537116147202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068247185277541</v>
+        <v>0.006794605080025641</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013724e-05</v>
+        <v>4.994743146261051e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757329</v>
+        <v>0.0006838103179389185</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999296858757</v>
+        <v>0.120999928142683</v>
       </c>
     </row>
     <row r="8">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.266560753660517</v>
+        <v>-3.322612164826406</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.398233586216479</v>
+        <v>-3.453980754773887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732812</v>
+        <v>0.002929998153368313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817044</v>
+        <v>0.006741165419815814</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413858e-05</v>
+        <v>4.897357410629079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970094</v>
+        <v>0.0006485265645910469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999274301907</v>
+        <v>0.1209999262355992</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.122292065062914</v>
+        <v>-2.330943279931203</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.335170936362396</v>
+        <v>-2.535803187345466</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120159</v>
+        <v>0.07560197571260402</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007295776788435114</v>
+        <v>0.007220209186640569</v>
       </c>
       <c r="H9" t="n">
-        <v>6.31833902711806e-05</v>
+        <v>6.140793176238142e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839523</v>
+        <v>0.0009763654809467796</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999537257347</v>
+        <v>0.120999949102309</v>
       </c>
     </row>
     <row r="10">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.741163168163421</v>
+        <v>-2.884628621011435</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.907944271045579</v>
+        <v>-3.045882740556624</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602928</v>
+        <v>0.03230111592600439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626189</v>
+        <v>0.007049964221656469</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367419e-05</v>
+        <v>5.683386960572569e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770122</v>
+        <v>0.0008462692644841026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999394412113</v>
+        <v>0.1209999362634382</v>
       </c>
     </row>
     <row r="11">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.128283276871695</v>
+        <v>-3.193232312434191</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2626381943586</v>
+        <v>-3.327352460618225</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00575644878960622</v>
+        <v>0.00556556873205253</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00682078993329</v>
+        <v>0.006801557732157556</v>
       </c>
       <c r="H11" t="n">
-        <v>5.136640220355119e-05</v>
+        <v>5.102742425733942e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000726381935528901</v>
+        <v>0.000702065250868961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999304262754</v>
+        <v>0.1209999290446966</v>
       </c>
     </row>
   </sheetData>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.078755569426559</v>
+        <v>-1.331034739893006</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.311972877418286</v>
+        <v>-1.557337059479754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1035855209040977</v>
+        <v>0.09678259603512485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007426784120860984</v>
+        <v>0.007360584415200119</v>
       </c>
       <c r="H2" t="n">
-        <v>6.745209067444211e-05</v>
+        <v>6.59915156572896e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00113757451685795</v>
+        <v>0.001093176782134807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999763592355</v>
+        <v>0.1209999708386309</v>
       </c>
     </row>
     <row r="3">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.378189043694081</v>
+        <v>-1.643125194728865</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.609239108032824</v>
+        <v>-1.865724913604531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1015010861438635</v>
+        <v>0.09317211825438219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007384459751810814</v>
+        <v>0.007311495997932799</v>
       </c>
       <c r="H3" t="n">
-        <v>6.548444499546888e-05</v>
+        <v>6.382090465884193e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001099064039383354</v>
+        <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999699586899</v>
+        <v>0.1209999641308979</v>
       </c>
     </row>
     <row r="4">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.601287658722098</v>
+        <v>-1.853047334293374</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.827543803081649</v>
+        <v>-2.070757641496643</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09677604689761529</v>
+        <v>0.08835730183707283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007353794018928255</v>
+        <v>0.007276274024719108</v>
       </c>
       <c r="H4" t="n">
-        <v>6.55098695919754e-05</v>
+        <v>6.376829510261294e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001060828464859125</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.120999965108556</v>
+        <v>0.1209999595581375</v>
       </c>
     </row>
     <row r="5">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.791296104189118</v>
+        <v>-1.995492025586752</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.007754316124651</v>
+        <v>-2.205153077324939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08711027253666284</v>
+        <v>0.08042508548545475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277042766543525</v>
+        <v>0.007207831033124094</v>
       </c>
       <c r="H5" t="n">
-        <v>6.531025410856539e-05</v>
+        <v>6.386321456211526e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001005625542878534</v>
+        <v>0.0009643156678152186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999608353387</v>
+        <v>0.1209999563372306</v>
       </c>
     </row>
     <row r="6">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.571897764041717</v>
+        <v>-2.686494854158044</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.72850887477563</v>
+        <v>-2.840776479108494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02782467977442239</v>
+        <v>0.02556995385670486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006933990820621253</v>
+        <v>0.006892784966531855</v>
       </c>
       <c r="H6" t="n">
-        <v>5.328554056626459e-05</v>
+        <v>5.236811283617112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007992118159823028</v>
+        <v>0.0007665777182855944</v>
       </c>
       <c r="J6" t="n">
-        <v>0.120999942782321</v>
+        <v>0.1209999402960915</v>
       </c>
     </row>
     <row r="7">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.957954152714411</v>
+        <v>-3.028167472580477</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.094738043204731</v>
+        <v>-3.164436305125848</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008197098928099425</v>
+        <v>0.007740537116147202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068247185277541</v>
+        <v>0.006794605080025641</v>
       </c>
       <c r="H7" t="n">
-        <v>5.058758619013724e-05</v>
+        <v>4.994743146261051e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007115513488757329</v>
+        <v>0.0006838103179389185</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999340994004</v>
+        <v>0.1209999325997964</v>
       </c>
     </row>
     <row r="8">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.085793088020571</v>
+        <v>-3.139360830841242</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.217465924409018</v>
+        <v>-3.270729424673915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003188815024732812</v>
+        <v>0.002929998153368313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006763638394817044</v>
+        <v>0.006741165419815814</v>
       </c>
       <c r="H8" t="n">
-        <v>4.944316302413858e-05</v>
+        <v>4.897357410629079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006710085431970094</v>
+        <v>0.0006485265645910469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999312626766</v>
+        <v>0.1209999301207918</v>
       </c>
     </row>
     <row r="9">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2008,25 +2008,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.682490535293083</v>
+        <v>-1.925320584947164</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.895369415916696</v>
+        <v>-2.130180500961102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08349467576120159</v>
+        <v>0.07560197571260402</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007295776788435114</v>
+        <v>0.007220209186640569</v>
       </c>
       <c r="H9" t="n">
-        <v>6.31833902711806e-05</v>
+        <v>6.140793176238142e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025281633839523</v>
+        <v>0.0009763654809467796</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999630498659</v>
+        <v>0.1209999577019838</v>
       </c>
     </row>
     <row r="10">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2044,25 +2044,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.416226594552518</v>
+        <v>-2.584068611167933</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.583007704323732</v>
+        <v>-2.745322737085341</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03770430310602928</v>
+        <v>0.03230111592600439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007124428452626189</v>
+        <v>0.007049964221656469</v>
       </c>
       <c r="H10" t="n">
-        <v>5.859710161367419e-05</v>
+        <v>5.683386960572569e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008938347806770122</v>
+        <v>0.0008462692644841026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999463302669</v>
+        <v>0.1209999426356574</v>
       </c>
     </row>
     <row r="11">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>ethylene, MTO; methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.088327305284071</v>
+        <v>-3.008378414293267</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.222682223618108</v>
+        <v>-3.142498566396469</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00575644878960622</v>
+        <v>0.00556556873205253</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00682078993329</v>
+        <v>0.006801557732157556</v>
       </c>
       <c r="H11" t="n">
-        <v>5.136640220355119e-05</v>
+        <v>5.102742425733942e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000726381935528901</v>
+        <v>0.000702065250868961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999312734085</v>
+        <v>0.1209999329638651</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
@@ -565,25 +565,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.10681000661595</v>
+        <v>2.106810006615949</v>
       </c>
       <c r="E4" t="n">
-        <v>1.889099615459105</v>
+        <v>1.889099615459103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08835730183707283</v>
+        <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719108</v>
+        <v>0.007276274024719035</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261294e-05</v>
+        <v>6.376829510261303e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237106</v>
+        <v>0.001013003488237104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000435117131</v>
+        <v>0.1210000435117151</v>
       </c>
     </row>
     <row r="5">
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.082490632459138</v>
+        <v>2.082490632459135</v>
       </c>
       <c r="E5" t="n">
-        <v>1.872829494262928</v>
+        <v>1.872829494262924</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545475</v>
+        <v>0.08042508548545471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124094</v>
+        <v>0.007207831033124156</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211526e-05</v>
+        <v>6.386321456211524e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152186</v>
+        <v>0.0009643156678152195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121000042795254</v>
+        <v>0.1210000427952544</v>
       </c>
     </row>
     <row r="6">
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.355731181612598</v>
+        <v>1.355731181612599</v>
       </c>
       <c r="E4" t="n">
-        <v>1.138020806379505</v>
+        <v>1.138020806379506</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08835730183707283</v>
+        <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719108</v>
+        <v>0.007276274024719035</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261294e-05</v>
+        <v>6.376829510261303e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237106</v>
+        <v>0.001013003488237104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000275879606</v>
+        <v>0.1210000275879624</v>
       </c>
     </row>
     <row r="5">
@@ -1025,22 +1025,22 @@
         <v>1.313157161422697</v>
       </c>
       <c r="E5" t="n">
-        <v>1.103496039537263</v>
+        <v>1.103496039537259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545475</v>
+        <v>0.08042508548545471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124094</v>
+        <v>0.007207831033124156</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211526e-05</v>
+        <v>6.386321456211524e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152186</v>
+        <v>0.0009643156678152195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000264844782</v>
+        <v>0.121000026484481</v>
       </c>
     </row>
     <row r="6">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.196242301074677</v>
+        <v>-2.196242301074716</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.413952601001734</v>
+        <v>-2.413952601001812</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08835730183707283</v>
+        <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719108</v>
+        <v>0.007276274024719035</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261294e-05</v>
+        <v>6.376829510261303e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237106</v>
+        <v>0.001013003488237104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999522819252</v>
+        <v>0.1209999522819643</v>
       </c>
     </row>
     <row r="5">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.290140281347844</v>
+        <v>-2.290140281347817</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.499801326839144</v>
+        <v>-2.499801326839115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545475</v>
+        <v>0.08042508548545471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124094</v>
+        <v>0.007207831033124156</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211526e-05</v>
+        <v>6.386321456211524e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152186</v>
+        <v>0.0009643156678152195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999500903445</v>
+        <v>0.1209999500903423</v>
       </c>
     </row>
     <row r="6">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.853047334293374</v>
+        <v>-1.853047334293452</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.070757641496643</v>
+        <v>-2.070757641496614</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08835730183707283</v>
+        <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719108</v>
+        <v>0.007276274024719035</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261294e-05</v>
+        <v>6.376829510261303e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237106</v>
+        <v>0.001013003488237104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999595581375</v>
+        <v>0.1209999595580309</v>
       </c>
     </row>
     <row r="5">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.995492025586752</v>
+        <v>-1.995492025586817</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.205153077324939</v>
+        <v>-2.205153077325011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545475</v>
+        <v>0.08042508548545471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124094</v>
+        <v>0.007207831033124156</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211526e-05</v>
+        <v>6.386321456211524e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152186</v>
+        <v>0.0009643156678152195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999563372306</v>
+        <v>0.1209999563372377</v>
       </c>
     </row>
     <row r="6">

--- a/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ethylene/ethylene climate change breakdown results.xlsx
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.141035566516668</v>
+        <v>2.141035566516666</v>
       </c>
       <c r="E2" t="n">
-        <v>1.914733173317971</v>
+        <v>1.914733173317972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09678259603512485</v>
+        <v>0.09678259603512486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007360584415200119</v>
+        <v>0.007360584415200049</v>
       </c>
       <c r="H2" t="n">
-        <v>6.59915156572896e-05</v>
+        <v>6.599151565728959e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001093176782134807</v>
+        <v>0.001093176782134811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000444505801</v>
+        <v>0.1210000444505774</v>
       </c>
     </row>
     <row r="3">
@@ -529,25 +529,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.124140124465378</v>
+        <v>2.12414012446538</v>
       </c>
       <c r="E3" t="n">
-        <v>1.901540325719272</v>
+        <v>1.901540325719273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09317211825438219</v>
+        <v>0.0931721182543824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007311495997932799</v>
+        <v>0.007311495997932803</v>
       </c>
       <c r="H3" t="n">
-        <v>6.382090465884193e-05</v>
+        <v>6.3820904658842e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000440013377</v>
+        <v>0.121000044001339</v>
       </c>
     </row>
     <row r="4">
@@ -574,16 +574,16 @@
         <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719035</v>
+        <v>0.007276274024719057</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261303e-05</v>
+        <v>6.3768295102613e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237104</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000435117151</v>
+        <v>0.1210000435117145</v>
       </c>
     </row>
     <row r="5">
@@ -607,16 +607,16 @@
         <v>1.872829494262924</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545471</v>
+        <v>0.08042508548545464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124156</v>
+        <v>0.007207831033124106</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211524e-05</v>
+        <v>6.386321456211521e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152195</v>
+        <v>0.0009643156678152181</v>
       </c>
       <c r="J5" t="n">
         <v>0.1210000427952544</v>
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.914707854784179</v>
+        <v>1.914707854784178</v>
       </c>
       <c r="E6" t="n">
         <v>1.760426132282819</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02556995385670486</v>
+        <v>0.02556995385670487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006892784966531855</v>
+        <v>0.006892784966531789</v>
       </c>
       <c r="H6" t="n">
-        <v>5.236811283617112e-05</v>
+        <v>5.236811283617114e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007665777182855944</v>
+        <v>0.0007665777182855939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000378470011</v>
+        <v>0.1210000378470006</v>
       </c>
     </row>
     <row r="7">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.854429677059307</v>
+        <v>1.854429677059306</v>
       </c>
       <c r="E7" t="n">
-        <v>1.718160740997224</v>
+        <v>1.718160740997223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007740537116147202</v>
+        <v>0.007740537116147196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006794605080025641</v>
+        <v>0.006794605080025659</v>
       </c>
       <c r="H7" t="n">
-        <v>4.994743146261051e-05</v>
+        <v>4.994743146261055e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006838103179389185</v>
+        <v>0.0006838103179389202</v>
       </c>
       <c r="J7" t="n">
         <v>0.1210000361165082</v>
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.835195175894396</v>
+        <v>1.835195175894395</v>
       </c>
       <c r="E8" t="n">
         <v>1.703826476595302</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002929998153368313</v>
+        <v>0.002929998153368323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006741165419815814</v>
+        <v>0.006741165419815804</v>
       </c>
       <c r="H8" t="n">
-        <v>4.897357410629079e-05</v>
+        <v>4.897357410629082e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006485265645910469</v>
+        <v>0.000648526564591048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000355872125</v>
+        <v>0.1210000355872118</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.067952962974462</v>
+        <v>2.067952962974463</v>
       </c>
       <c r="E9" t="n">
-        <v>1.863092962298436</v>
+        <v>1.863092962298437</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07560197571260402</v>
+        <v>0.07560197571260388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007220209186640569</v>
+        <v>0.007220209186640531</v>
       </c>
       <c r="H9" t="n">
-        <v>6.140793176238142e-05</v>
+        <v>6.140793176238143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009763654809467796</v>
+        <v>0.0009763654809467764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000423640722</v>
+        <v>0.1210000423640727</v>
       </c>
     </row>
     <row r="10">
@@ -781,25 +781,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.939107922231703</v>
+        <v>1.939107922231701</v>
       </c>
       <c r="E10" t="n">
         <v>1.777853700417632</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03230111592600439</v>
+        <v>0.0323011159260043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007049964221656469</v>
+        <v>0.007049964221656446</v>
       </c>
       <c r="H10" t="n">
-        <v>5.683386960572569e-05</v>
+        <v>5.683386960572572e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008462692644841026</v>
+        <v>0.0008462692644841051</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000385323198</v>
+        <v>0.1210000385323187</v>
       </c>
     </row>
     <row r="11">
@@ -823,16 +823,16 @@
         <v>1.721522999261031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00556556873205253</v>
+        <v>0.005565568732052526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006801557732157556</v>
+        <v>0.006801557732157549</v>
       </c>
       <c r="H11" t="n">
-        <v>5.102742425733942e-05</v>
+        <v>5.102742425733945e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000702065250868961</v>
+        <v>0.000702065250868957</v>
       </c>
       <c r="J11" t="n">
         <v>0.1210000360867771</v>
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.408386574731458</v>
+        <v>1.408386574731457</v>
       </c>
       <c r="E2" t="n">
-        <v>1.182084197065787</v>
+        <v>1.182084197065786</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09678259603512485</v>
+        <v>0.09678259603512486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007360584415200119</v>
+        <v>0.007360584415200049</v>
       </c>
       <c r="H2" t="n">
-        <v>6.59915156572896e-05</v>
+        <v>6.599151565728959e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001093176782134807</v>
+        <v>0.001093176782134811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000289175541</v>
+        <v>0.1210000289175543</v>
       </c>
     </row>
     <row r="3">
@@ -950,25 +950,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.384180269173959</v>
+        <v>1.38418026917396</v>
       </c>
       <c r="E3" t="n">
-        <v>1.161580486115878</v>
+        <v>1.161580486115881</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09317211825438219</v>
+        <v>0.0931721182543824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007311495997932799</v>
+        <v>0.007311495997932803</v>
       </c>
       <c r="H3" t="n">
-        <v>6.382090465884193e-05</v>
+        <v>6.3820904658842e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.121000028313313</v>
+        <v>0.1210000283133117</v>
       </c>
     </row>
     <row r="4">
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.355731181612599</v>
+        <v>1.355731181612597</v>
       </c>
       <c r="E4" t="n">
-        <v>1.138020806379506</v>
+        <v>1.138020806379507</v>
       </c>
       <c r="F4" t="n">
         <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719035</v>
+        <v>0.007276274024719057</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261303e-05</v>
+        <v>6.3768295102613e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237104</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000275879624</v>
+        <v>0.1210000275879586</v>
       </c>
     </row>
     <row r="5">
@@ -1025,22 +1025,22 @@
         <v>1.313157161422697</v>
       </c>
       <c r="E5" t="n">
-        <v>1.103496039537259</v>
+        <v>1.103496039537261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545471</v>
+        <v>0.08042508548545464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124156</v>
+        <v>0.007207831033124106</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211524e-05</v>
+        <v>6.386321456211521e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152195</v>
+        <v>0.0009643156678152181</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121000026484481</v>
+        <v>0.1210000264844804</v>
       </c>
     </row>
     <row r="6">
@@ -1061,22 +1061,22 @@
         <v>1.011279632097182</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8569979287495623</v>
+        <v>0.8569979287495605</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02556995385670486</v>
+        <v>0.02556995385670487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006892784966531855</v>
+        <v>0.006892784966531789</v>
       </c>
       <c r="H6" t="n">
-        <v>5.236811283617112e-05</v>
+        <v>5.236811283617114e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007665777182855944</v>
+        <v>0.0007665777182855939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000186932609</v>
+        <v>0.1210000186932628</v>
       </c>
     </row>
     <row r="7">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9081448545472069</v>
+        <v>0.9081448545472072</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7718759385474721</v>
+        <v>0.7718759385474714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007740537116147202</v>
+        <v>0.007740537116147196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006794605080025641</v>
+        <v>0.006794605080025659</v>
       </c>
       <c r="H7" t="n">
-        <v>4.994743146261051e-05</v>
+        <v>4.994743146261055e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006838103179389185</v>
+        <v>0.0006838103179389202</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000160541606</v>
+        <v>0.1210000160541614</v>
       </c>
     </row>
     <row r="8">
@@ -1130,25 +1130,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.878874847889285</v>
+        <v>0.8788748478892836</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7475061688653075</v>
+        <v>0.7475061688653064</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002929998153368313</v>
+        <v>0.002929998153368323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006741165419815814</v>
+        <v>0.006741165419815804</v>
       </c>
       <c r="H8" t="n">
-        <v>4.897357410629079e-05</v>
+        <v>4.897357410629082e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006485265645910469</v>
+        <v>0.000648526564591048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.121000015312096</v>
+        <v>0.1210000153120957</v>
       </c>
     </row>
     <row r="9">
@@ -1169,22 +1169,22 @@
         <v>1.285591915371015</v>
       </c>
       <c r="E9" t="n">
-        <v>1.080731931281963</v>
+        <v>1.080731931281964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07560197571260402</v>
+        <v>0.07560197571260388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007220209186640569</v>
+        <v>0.007220209186640531</v>
       </c>
       <c r="H9" t="n">
-        <v>6.140793176238142e-05</v>
+        <v>6.140793176238143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009763654809467796</v>
+        <v>0.0009763654809467764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000257770985</v>
+        <v>0.1210000257770982</v>
       </c>
     </row>
     <row r="10">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.049040512915575</v>
+        <v>1.049040512915574</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8877863099719849</v>
+        <v>0.8877863099719838</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03230111592600439</v>
+        <v>0.0323011159260043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007049964221656469</v>
+        <v>0.007049964221656446</v>
       </c>
       <c r="H10" t="n">
-        <v>5.683386960572569e-05</v>
+        <v>5.683386960572572e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008462692644841026</v>
+        <v>0.0008462692644841051</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000196618395</v>
+        <v>0.12100001966184</v>
       </c>
     </row>
     <row r="11">
@@ -1238,25 +1238,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9020524648194492</v>
+        <v>0.9020524648194487</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7679322298105761</v>
+        <v>0.7679322298105763</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00556556873205253</v>
+        <v>0.005565568732052526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006801557732157556</v>
+        <v>0.006801557732157549</v>
       </c>
       <c r="H11" t="n">
-        <v>5.102742425733942e-05</v>
+        <v>5.102742425733945e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000702065250868961</v>
+        <v>0.000702065250868957</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000158695369</v>
+        <v>0.1210000158695361</v>
       </c>
     </row>
   </sheetData>
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.913735852460093</v>
+        <v>-1.913735852460067</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.140038159692896</v>
+        <v>-2.14003815969284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09678259603512485</v>
+        <v>0.09678259603512486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007360584415200119</v>
+        <v>0.007360584415200049</v>
       </c>
       <c r="H2" t="n">
-        <v>6.59915156572896e-05</v>
+        <v>6.599151565728959e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001093176782134807</v>
+        <v>0.001093176782134811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999584846859</v>
+        <v>0.1209999584846566</v>
       </c>
     </row>
     <row r="3">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.066027288397335</v>
+        <v>-2.06602728839734</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.288626998306958</v>
+        <v>-2.28862699830686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09317211825438219</v>
+        <v>0.0931721182543824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007311495997932799</v>
+        <v>0.007311495997932803</v>
       </c>
       <c r="H3" t="n">
-        <v>6.382090465884193e-05</v>
+        <v>6.3820904658842e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999551648555</v>
+        <v>0.120999955164752</v>
       </c>
     </row>
     <row r="4">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.196242301074716</v>
+        <v>-2.196242301074822</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.413952601001812</v>
+        <v>-2.413952601001864</v>
       </c>
       <c r="F4" t="n">
         <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719035</v>
+        <v>0.007276274024719057</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261303e-05</v>
+        <v>6.3768295102613e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237104</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999522819643</v>
+        <v>0.120999952281911</v>
       </c>
     </row>
     <row r="5">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.290140281347817</v>
+        <v>-2.290140281347883</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.499801326839115</v>
+        <v>-2.499801326839055</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545471</v>
+        <v>0.08042508548545464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124156</v>
+        <v>0.007207831033124106</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211524e-05</v>
+        <v>6.386321456211521e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152195</v>
+        <v>0.0009643156678152181</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999500903423</v>
+        <v>0.1209999500902157</v>
       </c>
     </row>
     <row r="6">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.95144306735271</v>
+        <v>-2.951443067352702</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.105724686685964</v>
+        <v>-3.105724686685949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02556995385670486</v>
+        <v>0.02556995385670487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006892784966531855</v>
+        <v>0.006892784966531789</v>
       </c>
       <c r="H6" t="n">
-        <v>5.236811283617112e-05</v>
+        <v>5.236811283617114e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007665777182855944</v>
+        <v>0.0007665777182855939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.120999934678895</v>
+        <v>0.1209999346788884</v>
       </c>
     </row>
     <row r="7">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.238392115823753</v>
+        <v>-3.238392115823702</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.374660943912011</v>
+        <v>-3.374660943912027</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007740537116147202</v>
+        <v>0.007740537116147196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006794605080025641</v>
+        <v>0.006794605080025659</v>
       </c>
       <c r="H7" t="n">
-        <v>4.994743146261051e-05</v>
+        <v>4.994743146261055e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006838103179389185</v>
+        <v>0.0006838103179389202</v>
       </c>
       <c r="J7" t="n">
-        <v>0.120999928142683</v>
+        <v>0.1209999281427505</v>
       </c>
     </row>
     <row r="8">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.322612164826406</v>
+        <v>-3.322612164826353</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.453980754773887</v>
+        <v>-3.453980754773869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002929998153368313</v>
+        <v>0.002929998153368323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006741165419815814</v>
+        <v>0.006741165419815804</v>
       </c>
       <c r="H8" t="n">
-        <v>4.897357410629079e-05</v>
+        <v>4.897357410629082e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006485265645910469</v>
+        <v>0.000648526564591048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999262355992</v>
+        <v>0.1209999262356343</v>
       </c>
     </row>
     <row r="9">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.330943279931203</v>
+        <v>-2.330943279931248</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.535803187345466</v>
+        <v>-2.535803187345462</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07560197571260402</v>
+        <v>0.07560197571260388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007220209186640569</v>
+        <v>0.007220209186640531</v>
       </c>
       <c r="H9" t="n">
-        <v>6.140793176238142e-05</v>
+        <v>6.140793176238143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009763654809467796</v>
+        <v>0.0009763654809467764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.120999949102309</v>
+        <v>0.1209999491022602</v>
       </c>
     </row>
     <row r="10">
@@ -1626,22 +1626,22 @@
         <v>-2.884628621011435</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.045882740556624</v>
+        <v>-3.045882740556653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03230111592600439</v>
+        <v>0.0323011159260043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007049964221656469</v>
+        <v>0.007049964221656446</v>
       </c>
       <c r="H10" t="n">
-        <v>5.683386960572569e-05</v>
+        <v>5.683386960572572e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008462692644841026</v>
+        <v>0.0008462692644841051</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999362634382</v>
+        <v>0.1209999362634671</v>
       </c>
     </row>
     <row r="11">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.193232312434191</v>
+        <v>-3.193232312434142</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.327352460618225</v>
+        <v>-3.327352460618179</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00556556873205253</v>
+        <v>0.005565568732052526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006801557732157556</v>
+        <v>0.006801557732157549</v>
       </c>
       <c r="H11" t="n">
-        <v>5.102742425733942e-05</v>
+        <v>5.102742425733945e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000702065250868961</v>
+        <v>0.000702065250868957</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999290446966</v>
+        <v>0.1209999290447001</v>
       </c>
     </row>
   </sheetData>
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.331034739893006</v>
+        <v>-1.331034739892968</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.557337059479754</v>
+        <v>-1.557337059479694</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09678259603512485</v>
+        <v>0.09678259603512486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007360584415200119</v>
+        <v>0.007360584415200049</v>
       </c>
       <c r="H2" t="n">
-        <v>6.59915156572896e-05</v>
+        <v>6.599151565728959e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001093176782134807</v>
+        <v>0.001093176782134811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999708386309</v>
+        <v>0.1209999708386094</v>
       </c>
     </row>
     <row r="3">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.643125194728865</v>
+        <v>-1.64312519472884</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.865724913604531</v>
+        <v>-1.865724913604502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09317211825438219</v>
+        <v>0.0931721182543824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007311495997932799</v>
+        <v>0.007311495997932803</v>
       </c>
       <c r="H3" t="n">
-        <v>6.382090465884193e-05</v>
+        <v>6.3820904658842e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.001052319587794022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999641308979</v>
+        <v>0.1209999641308934</v>
       </c>
     </row>
     <row r="4">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.853047334293452</v>
+        <v>-1.853047334293441</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.070757641496614</v>
+        <v>-2.0707576414967</v>
       </c>
       <c r="F4" t="n">
         <v>0.08835730183707277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007276274024719035</v>
+        <v>0.007276274024719057</v>
       </c>
       <c r="H4" t="n">
-        <v>6.376829510261303e-05</v>
+        <v>6.3768295102613e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001013003488237104</v>
+        <v>0.001013003488237106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999595580309</v>
+        <v>0.120999959558127</v>
       </c>
     </row>
     <row r="5">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.995492025586817</v>
+        <v>-1.995492025586832</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.205153077325011</v>
+        <v>-2.205153077325057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08042508548545471</v>
+        <v>0.08042508548545464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007207831033124156</v>
+        <v>0.007207831033124106</v>
       </c>
       <c r="H5" t="n">
-        <v>6.386321456211524e-05</v>
+        <v>6.386321456211521e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009643156678152195</v>
+        <v>0.0009643156678152181</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999563372377</v>
+        <v>0.1209999563372692</v>
       </c>
     </row>
     <row r="6">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.686494854158044</v>
+        <v>-2.686494854158033</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.840776479108494</v>
+        <v>-2.840776479108472</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02556995385670486</v>
+        <v>0.02556995385670487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006892784966531855</v>
+        <v>0.006892784966531789</v>
       </c>
       <c r="H6" t="n">
-        <v>5.236811283617112e-05</v>
+        <v>5.236811283617114e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007665777182855944</v>
+        <v>0.0007665777182855939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999402960915</v>
+        <v>0.12099994029608</v>
       </c>
     </row>
     <row r="7">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.028167472580477</v>
+        <v>-3.028167472580478</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.164436305125848</v>
+        <v>-3.164436305125781</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007740537116147202</v>
+        <v>0.007740537116147196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006794605080025641</v>
+        <v>0.006794605080025659</v>
       </c>
       <c r="H7" t="n">
-        <v>4.994743146261051e-05</v>
+        <v>4.994743146261055e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006838103179389185</v>
+        <v>0.0006838103179389202</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999325997964</v>
+        <v>0.1209999325997284</v>
       </c>
     </row>
     <row r="8">
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.139360830841242</v>
+        <v>-3.139360830841225</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.270729424673915</v>
+        <v>-3.270729424673872</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002929998153368313</v>
+        <v>0.002929998153368323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006741165419815814</v>
+        <v>0.006741165419815804</v>
       </c>
       <c r="H8" t="n">
-        <v>4.897357410629079e-05</v>
+        <v>4.897357410629082e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006485265645910469</v>
+        <v>0.000648526564591048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999301207918</v>
+        <v>0.120999930120766</v>
       </c>
     </row>
     <row r="9">
@@ -2008,25 +2008,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.925320584947164</v>
+        <v>-1.925320584947254</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.130180500961102</v>
+        <v>-2.130180500961107</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07560197571260402</v>
+        <v>0.07560197571260388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007220209186640569</v>
+        <v>0.007220209186640531</v>
       </c>
       <c r="H9" t="n">
-        <v>6.140793176238142e-05</v>
+        <v>6.140793176238143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009763654809467796</v>
+        <v>0.0009763654809467764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999577019838</v>
+        <v>0.120999957701899</v>
       </c>
     </row>
     <row r="10">
@@ -2044,25 +2044,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.584068611167933</v>
+        <v>-2.584068611167887</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.745322737085341</v>
+        <v>-2.745322737085283</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03230111592600439</v>
+        <v>0.0323011159260043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007049964221656469</v>
+        <v>0.007049964221656446</v>
       </c>
       <c r="H10" t="n">
-        <v>5.683386960572569e-05</v>
+        <v>5.683386960572572e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008462692644841026</v>
+        <v>0.0008462692644841051</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999426356574</v>
+        <v>0.120999942635645</v>
       </c>
     </row>
     <row r="11">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.008378414293267</v>
+        <v>-3.008378414293221</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.142498566396469</v>
+        <v>-3.142498566396358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00556556873205253</v>
+        <v>0.005565568732052526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006801557732157556</v>
+        <v>0.006801557732157549</v>
       </c>
       <c r="H11" t="n">
-        <v>5.102742425733942e-05</v>
+        <v>5.102742425733945e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000702065250868961</v>
+        <v>0.000702065250868957</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999329638651</v>
+        <v>0.1209999329638007</v>
       </c>
     </row>
   </sheetData>
